--- a/Result/profitability/1616.xlsx
+++ b/Result/profitability/1616.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="N2" t="n">
-        <v>13.05125</v>
+        <v>12.63625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.43875</v>
+        <v>0.27875</v>
       </c>
       <c r="N3" t="n">
-        <v>12.14</v>
+        <v>11.41125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2437499999999999</v>
+        <v>0.20125</v>
       </c>
       <c r="N4" t="n">
-        <v>10.84625</v>
+        <v>9.952500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.41</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.007500000000000034</v>
+        <v>-0.1062500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>7.46375</v>
+        <v>6.7475</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1300000000000001</v>
+        <v>-0.16875</v>
       </c>
       <c r="N6" t="n">
-        <v>6.43375</v>
+        <v>5.58875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22875</v>
+        <v>-0.1125000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>4.84875</v>
+        <v>4.356249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14875</v>
+        <v>-0.1512500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>4.02</v>
+        <v>3.9225</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,10 +2026,10 @@
         <v>0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08500000000000005</v>
+        <v>-0.08500000000000008</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3225</v>
+        <v>4.322500000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1616</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1486</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1351</v>
+      </c>
+      <c r="E75" t="n">
+        <v>135</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>92</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.17%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>70</v>
+      </c>
+      <c r="K75" t="n">
+        <v>48</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.26875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.07142857142857151</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7799999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07910750507099384</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7523809523809524</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.73</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.386900742741391</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
